--- a/docs/xlsx/jobs-2026-08-30.xlsx
+++ b/docs/xlsx/jobs-2026-08-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,34 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>Prescott Circus Theatre</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 72800.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef0f8f11bec940fab62e23d171bf2831-operations-manager-prescott-circus-theatre-oakland</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +75,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +101,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +540,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +579,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-08-30.xlsx
+++ b/docs/xlsx/jobs-2026-08-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
   <si>
     <t>Title</t>
   </si>
@@ -59,6 +59,24 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/ef0f8f11bec940fab62e23d171bf2831-operations-manager-prescott-circus-theatre-oakland</t>
+  </si>
+  <si>
+    <t>Pathways to Work Program Manager</t>
+  </si>
+  <si>
+    <t>Homeless Garden Project</t>
+  </si>
+  <si>
+    <t>Santa Cruz, California</t>
+  </si>
+  <si>
+    <t>USD 64480.00 - 69000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b5a99ce8e654b6da1f8c93740cb9a26-pathways-to-work-program-manager-homeless-garden-project-santa-cruz</t>
   </si>
 </sst>
 </file>
@@ -540,7 +558,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -602,10 +620,34 @@
         <v>14</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
